--- a/test-case-exports/Login.xlsx
+++ b/test-case-exports/Login.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="241">
   <si>
     <t>#</t>
   </si>
@@ -146,7 +146,7 @@
     <t>API-04: should return 200 with valid OTP (dev env — OTP is 00000000)</t>
   </si>
   <si>
-    <t>conditionally skipped at runtime if !accessToken — Sign-in did not return an accessToken — skipping OTP verification</t>
+    <t>Gated: Sign-in did not return an accessToken — skipping OTP verification</t>
   </si>
   <si>
     <t>API-N11: should return 401 with an incorrect OTP</t>
@@ -167,6 +167,114 @@
     <t>No</t>
   </si>
   <si>
+    <t>BusinessTestCases/Login/api/LoginNafathWathiqExpiry.spec.ts</t>
+  </si>
+  <si>
+    <t>Login – NAFATH document (National ID/Iqama) expired</t>
+  </si>
+  <si>
+    <t>NW-01: should return 409 when NAFATH document data has expired</t>
+  </si>
+  <si>
+    <t>Gated: Set NAFATH_EXPIRED_COMPANY and NAFATH_EXPIRED_MOBILE env vars to run this test</t>
+  </si>
+  <si>
+    <t>NW-01a: 409 response body should carry error code NAFATH_DATA_EXPIRED</t>
+  </si>
+  <si>
+    <t>NW-01b: error response should not expose stack traces or database details</t>
+  </si>
+  <si>
+    <t>Login – WATHIQ document (CRN) expired</t>
+  </si>
+  <si>
+    <t>NW-02: should return 409 when WATHIQ document data has expired</t>
+  </si>
+  <si>
+    <t>Gated: Set WATHIQ_EXPIRED_COMPANY and WATHIQ_EXPIRED_MOBILE env vars to run this test</t>
+  </si>
+  <si>
+    <t>NW-02a: 409 response body should carry error code WATHIQ_DATA_EXPIRED</t>
+  </si>
+  <si>
+    <t>NW-02b: error response should not expose stack traces or database details</t>
+  </si>
+  <si>
+    <t>Login – regression: unaffected account still logs in normally</t>
+  </si>
+  <si>
+    <t>NW-03: login should still succeed (200) for an account with no NAFATH/WATHIQ expiry</t>
+  </si>
+  <si>
+    <t>Login – NAFATH Redis TTL expired (document still valid)</t>
+  </si>
+  <si>
+    <t>NW-04: should return 409 distinguishing TTL/cache expiry from document expiry</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Skipped: pending DB access to confirm which entity (user vs. profile) was deactivated — not observable from the login API response alone, see EMI-5836</t>
+  </si>
+  <si>
+    <t>NW-05: should not require the user to physically re-present ID — only NAFATH Generate Random + Get Status re-verification</t>
+  </si>
+  <si>
+    <t>Login – WATHIQ Redis TTL expired (auto-heal, should NOT block login)</t>
+  </si>
+  <si>
+    <t>NW-06: login should succeed once the background TTL-monitoring job has refreshed WATHIQ data automatically</t>
+  </si>
+  <si>
+    <t>NW-07: login should be blocked with WATHIQ_DATA_EXPIRED if the TTL-refresh job discovers the CRN itself has since expired</t>
+  </si>
+  <si>
+    <t>Login – NAFATH revalidation flow (Generate Random + Get Status)</t>
+  </si>
+  <si>
+    <t>NW-08: successful re-verification should clear is_nafath_data_expired and allow login</t>
+  </si>
+  <si>
+    <t>NW-09: a failed/abandoned re-verification should leave the account blocked with 409 NAFATH_DATA_EXPIRED</t>
+  </si>
+  <si>
+    <t>Login – WATHIQ revalidation flow (refresh CRN)</t>
+  </si>
+  <si>
+    <t>NW-10: successful CRN refresh should clear is_wathiq_data_expired and allow login</t>
+  </si>
+  <si>
+    <t>NW-11: a refresh attempt that still returns an expired CRN should leave the account blocked with 409 WATHIQ_DATA_EXPIRED</t>
+  </si>
+  <si>
+    <t>Login – deactivation scope (per Amer Majed Abdalrazeq's 2026-07-16 comment)</t>
+  </si>
+  <si>
+    <t>NW-12: NAFATH expiry should deactivate the USER, not the individual business profile</t>
+  </si>
+  <si>
+    <t>NW-13: WATHIQ expiry should deactivate the PROFILE, not the user</t>
+  </si>
+  <si>
+    <t>Login – NAFATH / WATHIQ expiry message localisation (EMI-5969)</t>
+  </si>
+  <si>
+    <t>NW-14: the NAFATH_DATA_EXPIRED message is returned in Arabic when ar_sa is requested</t>
+  </si>
+  <si>
+    <t>Gated: set NAFATH_EXPIRED_COMPANY / NAFATH_EXPIRED_MOBILE to a blocked fixture account</t>
+  </si>
+  <si>
+    <t>NW-15: the WATHIQ_DATA_EXPIRED message is returned in Arabic when ar_sa is requested</t>
+  </si>
+  <si>
+    <t>Gated: set WATHIQ_EXPIRED_COMPANY / WATHIQ_EXPIRED_MOBILE to a blocked fixture account</t>
+  </si>
+  <si>
+    <t>NW-16: the en_uk and ar_sa responses differ, and the error CODE stays stable across both</t>
+  </si>
+  <si>
     <t>BusinessTestCases/Login/functional/LoginFormValidation.spec.ts</t>
   </si>
   <si>
@@ -290,9 +398,6 @@
     <t>should stay on the login page with a wrong password</t>
   </si>
   <si>
-    <t>route mocking</t>
-  </si>
-  <si>
     <t>should stay on the login page with a wrong company number</t>
   </si>
   <si>
@@ -335,10 +440,8 @@
     <t>should keep Log In button disabled when password contains only whitespace</t>
   </si>
   <si>
-    <t>Skipped</t>
-  </si>
-  <si>
-    <t>test.skip() on this test; route mocking</t>
+    <t xml:space="preserve">Skipped: async () =&gt; {
+        await loginPage.companyInput.fill(VALID_COMPANY</t>
   </si>
   <si>
     <t>should stay on the login page when correct company is paired with wrong mobile and wrong password</t>
@@ -362,9 +465,6 @@
     <t>should navigate to the Forgot Password page when the link is clicked</t>
   </si>
   <si>
-    <t>uses storageState</t>
-  </si>
-  <si>
     <t>should navigate to the Sign Up page when the link is clicked</t>
   </si>
   <si>
@@ -380,9 +480,6 @@
     <t>should redirect away from the login page when already logged in</t>
   </si>
   <si>
-    <t>test.skip() on this test; uses storageState</t>
-  </si>
-  <si>
     <t>should not display the Log In button when already logged in</t>
   </si>
   <si>
@@ -446,36 +543,30 @@
     <t>should redirect to dashboard after the validation card dismisses (when OTP is disabled)</t>
   </si>
   <si>
-    <t>conditionally skipped at runtime if otpAppeared — OTP is enabled in this environment — direct redirect is not applicable</t>
-  </si>
-  <si>
     <t>BusinessTestCases/Login/functional/LoginSecurity.spec.ts</t>
   </si>
   <si>
     <t>Login — Security</t>
   </si>
   <si>
+    <t>should return the same error response for a wrong company number and a wrong mobile number (prevents user enumeration)</t>
+  </si>
+  <si>
+    <t>should not execute a script payload entered in the company number field (XSS)</t>
+  </si>
+  <si>
+    <t>should not execute a script payload entered in the password field (XSS)</t>
+  </si>
+  <si>
+    <t>should send the login request via POST — credentials must not appear in the URL</t>
+  </si>
+  <si>
+    <t>should not expose stack traces or database details in failed login error responses</t>
+  </si>
+  <si>
     <t>should lock the account after 3 consecutive failed login attempts</t>
   </si>
   <si>
-    <t>conditionally skipped at runtime if !LOCKOUT_COMPANY || !LOCKOUT_MOBILE — Set LOCKOUT_COMPANY, LOCKOUT_MOBILE and LOCKOUT_PASSWORD env vars to run this test</t>
-  </si>
-  <si>
-    <t>should return the same error response for a wrong company number and a wrong mobile number (prevents user enumeration)</t>
-  </si>
-  <si>
-    <t>should not execute a script payload entered in the company number field (XSS)</t>
-  </si>
-  <si>
-    <t>should not execute a script payload entered in the password field (XSS)</t>
-  </si>
-  <si>
-    <t>should send the login request via POST — credentials must not appear in the URL</t>
-  </si>
-  <si>
-    <t>should not expose stack traces or database details in failed login error responses</t>
-  </si>
-  <si>
     <t>BusinessTestCases/Login/ui/LoginPage.spec.ts</t>
   </si>
   <si>
@@ -587,6 +678,9 @@
     <t>should show the "Just a moment..." heading</t>
   </si>
   <si>
+    <t>Skipped: loginPage)) === 'bypassed', SKIP_MSG</t>
+  </si>
+  <si>
     <t>should show the popup subtitle text</t>
   </si>
   <si>
@@ -605,7 +699,7 @@
     <t>should show the OTP dialog after the validation card completes (when OTP is enabled)</t>
   </si>
   <si>
-    <t>conditionally skipped at runtime if !otpAppeared — OTP is disabled in this environment — dialog does not appear</t>
+    <t>Gated: loginPage)) === 'bypassed', SKIP_MSG</t>
   </si>
   <si>
     <t>Summary — Login</t>
@@ -614,13 +708,13 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.275Z</t>
+    <t>2026-09-08T15:08:53.422Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>api</t>
@@ -638,7 +732,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -656,6 +753,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -665,7 +763,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -675,11 +773,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -697,8 +790,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1040,19 +1137,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I148"/>
+  <dimension ref="A1:I168"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,36 +1180,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1139,36 +1238,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1197,36 +1296,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1255,36 +1354,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1313,36 +1412,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1371,36 +1470,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1429,36 +1528,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1487,36 +1586,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1545,36 +1644,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1603,36 +1702,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1661,36 +1760,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1719,36 +1818,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1777,36 +1876,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1835,36 +1934,36 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="G28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1893,36 +1992,36 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1951,36 +2050,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1997,48 +2096,48 @@
         <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2049,13 +2148,13 @@
         <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>14</v>
@@ -2064,39 +2163,39 @@
         <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="D36" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2107,13 +2206,13 @@
         <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>14</v>
@@ -2122,39 +2221,39 @@
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D38" t="s">
-        <v>52</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2165,54 +2264,54 @@
         <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2223,54 +2322,54 @@
         <v>51</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D42" t="s">
-        <v>52</v>
-      </c>
-      <c r="E42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>63</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2281,54 +2380,54 @@
         <v>51</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D44" t="s">
-        <v>64</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="D44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2339,54 +2438,54 @@
         <v>51</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46">
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D46" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" t="s">
-        <v>68</v>
-      </c>
-      <c r="G46" t="s">
-        <v>14</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2397,54 +2496,54 @@
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D48" t="s">
-        <v>64</v>
-      </c>
-      <c r="E48" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" t="s">
-        <v>70</v>
-      </c>
-      <c r="G48" t="s">
-        <v>14</v>
-      </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2455,13 +2554,13 @@
         <v>51</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>14</v>
@@ -2470,39 +2569,39 @@
         <v>15</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D50" t="s">
-        <v>64</v>
-      </c>
-      <c r="E50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" t="s">
-        <v>72</v>
-      </c>
-      <c r="G50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2513,13 +2612,13 @@
         <v>51</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>14</v>
@@ -2528,39 +2627,39 @@
         <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" t="s">
-        <v>75</v>
-      </c>
-      <c r="G52" t="s">
-        <v>14</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2568,16 +2667,16 @@
         <v>9</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -2589,36 +2688,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54">
+    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>76</v>
-      </c>
-      <c r="D54" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" t="s">
-        <v>79</v>
-      </c>
-      <c r="G54" t="s">
-        <v>14</v>
-      </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2626,16 +2725,16 @@
         <v>9</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>14</v>
@@ -2647,36 +2746,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56">
+    <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" t="s">
-        <v>81</v>
-      </c>
-      <c r="G56" t="s">
-        <v>14</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2684,16 +2783,16 @@
         <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>14</v>
@@ -2705,36 +2804,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58">
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" t="s">
-        <v>77</v>
-      </c>
-      <c r="E58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" t="s">
-        <v>83</v>
-      </c>
-      <c r="G58" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2742,16 +2841,16 @@
         <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>14</v>
@@ -2763,36 +2862,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60">
+    <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>85</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2800,16 +2899,16 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>14</v>
@@ -2821,36 +2920,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62">
+    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G62" t="s">
-        <v>14</v>
-      </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D62" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2858,16 +2957,16 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>14</v>
@@ -2879,36 +2978,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64">
+    <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D64" t="s">
-        <v>90</v>
-      </c>
-      <c r="E64" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
-        <v>91</v>
-      </c>
-      <c r="G64" t="s">
-        <v>14</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2916,16 +3015,16 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>14</v>
@@ -2934,39 +3033,39 @@
         <v>15</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" t="s">
-        <v>90</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>94</v>
-      </c>
-      <c r="G66" t="s">
-        <v>14</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2974,16 +3073,16 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>14</v>
@@ -2992,39 +3091,39 @@
         <v>15</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>89</v>
-      </c>
-      <c r="D68" t="s">
-        <v>90</v>
-      </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>96</v>
-      </c>
-      <c r="G68" t="s">
-        <v>14</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3032,16 +3131,16 @@
         <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>14</v>
@@ -3050,39 +3149,39 @@
         <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>89</v>
-      </c>
-      <c r="D70" t="s">
-        <v>97</v>
-      </c>
-      <c r="E70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" t="s">
-        <v>99</v>
-      </c>
-      <c r="G70" t="s">
-        <v>14</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3090,16 +3189,16 @@
         <v>9</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>14</v>
@@ -3108,39 +3207,39 @@
         <v>15</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>89</v>
-      </c>
-      <c r="D72" t="s">
-        <v>97</v>
-      </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>101</v>
-      </c>
-      <c r="G72" t="s">
-        <v>14</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3148,16 +3247,16 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>14</v>
@@ -3166,39 +3265,39 @@
         <v>15</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
-        <v>89</v>
-      </c>
-      <c r="D74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E74" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" t="s">
-        <v>103</v>
-      </c>
-      <c r="G74" t="s">
-        <v>14</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3206,16 +3305,16 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>14</v>
@@ -3224,39 +3323,39 @@
         <v>15</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76" t="s">
-        <v>104</v>
-      </c>
-      <c r="E76" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" t="s">
-        <v>106</v>
-      </c>
-      <c r="G76" t="s">
-        <v>107</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3264,16 +3363,16 @@
         <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>14</v>
@@ -3282,39 +3381,39 @@
         <v>15</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" t="s">
-        <v>104</v>
-      </c>
-      <c r="E78" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" t="s">
-        <v>110</v>
-      </c>
-      <c r="G78" t="s">
-        <v>14</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3322,16 +3421,16 @@
         <v>9</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>14</v>
@@ -3340,39 +3439,39 @@
         <v>15</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80" t="s">
-        <v>104</v>
-      </c>
-      <c r="E80" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="B80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G80" t="s">
-        <v>14</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D80" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3380,16 +3479,16 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="E81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>14</v>
@@ -3398,39 +3497,39 @@
         <v>15</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D82" t="s">
-        <v>114</v>
-      </c>
-      <c r="E82" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" t="s">
-        <v>117</v>
-      </c>
-      <c r="G82" t="s">
-        <v>14</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3438,16 +3537,16 @@
         <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="E83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>14</v>
@@ -3456,39 +3555,39 @@
         <v>15</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>113</v>
-      </c>
-      <c r="D84" t="s">
-        <v>114</v>
-      </c>
-      <c r="E84" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s">
-        <v>119</v>
-      </c>
-      <c r="G84" t="s">
-        <v>14</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3496,57 +3595,57 @@
         <v>9</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D86" t="s">
-        <v>120</v>
-      </c>
-      <c r="E86" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" t="s">
-        <v>123</v>
-      </c>
-      <c r="G86" t="s">
-        <v>107</v>
-      </c>
-      <c r="H86" t="s">
-        <v>50</v>
-      </c>
-      <c r="I86" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3554,57 +3653,57 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" t="s">
-        <v>124</v>
-      </c>
-      <c r="D88" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F88" t="s">
-        <v>127</v>
-      </c>
-      <c r="G88" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3612,57 +3711,57 @@
         <v>9</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" t="s">
-        <v>124</v>
-      </c>
-      <c r="D90" t="s">
-        <v>125</v>
-      </c>
-      <c r="E90" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" t="s">
-        <v>129</v>
-      </c>
-      <c r="G90" t="s">
-        <v>14</v>
-      </c>
-      <c r="H90" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D90" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3670,57 +3769,57 @@
         <v>9</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" t="s">
-        <v>124</v>
-      </c>
-      <c r="D92" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" t="s">
-        <v>131</v>
-      </c>
-      <c r="G92" t="s">
-        <v>14</v>
-      </c>
-      <c r="H92" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D92" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -3728,57 +3827,57 @@
         <v>9</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>9</v>
-      </c>
-      <c r="C94" t="s">
-        <v>124</v>
-      </c>
-      <c r="D94" t="s">
-        <v>125</v>
-      </c>
-      <c r="E94" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" t="s">
-        <v>133</v>
-      </c>
-      <c r="G94" t="s">
-        <v>14</v>
-      </c>
-      <c r="H94" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -3786,57 +3885,57 @@
         <v>9</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" t="s">
-        <v>124</v>
-      </c>
-      <c r="D96" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" t="s">
-        <v>135</v>
-      </c>
-      <c r="G96" t="s">
-        <v>14</v>
-      </c>
-      <c r="H96" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D96" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -3844,57 +3943,57 @@
         <v>9</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" t="s">
-        <v>124</v>
-      </c>
-      <c r="D98" t="s">
-        <v>125</v>
-      </c>
-      <c r="E98" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" t="s">
-        <v>137</v>
-      </c>
-      <c r="G98" t="s">
-        <v>14</v>
-      </c>
-      <c r="H98" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D98" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -3902,57 +4001,57 @@
         <v>9</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>124</v>
-      </c>
-      <c r="D100" t="s">
-        <v>138</v>
-      </c>
-      <c r="E100" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" t="s">
-        <v>140</v>
-      </c>
-      <c r="G100" t="s">
-        <v>14</v>
-      </c>
-      <c r="H100" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -3960,16 +4059,16 @@
         <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>14</v>
@@ -3981,36 +4080,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102">
+    <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102" t="s">
-        <v>124</v>
-      </c>
-      <c r="D102" t="s">
-        <v>138</v>
-      </c>
-      <c r="E102" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" t="s">
-        <v>142</v>
-      </c>
-      <c r="G102" t="s">
-        <v>14</v>
-      </c>
-      <c r="H102" t="s">
-        <v>15</v>
-      </c>
-      <c r="I102" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -4018,16 +4117,16 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>14</v>
@@ -4036,39 +4135,39 @@
         <v>15</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
-        <v>9</v>
-      </c>
-      <c r="C104" t="s">
-        <v>145</v>
-      </c>
-      <c r="D104" t="s">
-        <v>146</v>
-      </c>
-      <c r="E104" t="s">
-        <v>12</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="B104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G104" t="s">
-        <v>14</v>
-      </c>
-      <c r="H104" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" t="s">
+      <c r="D104" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -4076,16 +4175,16 @@
         <v>9</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>14</v>
@@ -4097,36 +4196,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106">
+    <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" t="s">
-        <v>145</v>
-      </c>
-      <c r="D106" t="s">
-        <v>146</v>
-      </c>
-      <c r="E106" t="s">
-        <v>12</v>
-      </c>
-      <c r="F106" t="s">
-        <v>150</v>
-      </c>
-      <c r="G106" t="s">
-        <v>14</v>
-      </c>
-      <c r="H106" t="s">
-        <v>15</v>
-      </c>
-      <c r="I106" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -4134,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>14</v>
@@ -4155,36 +4254,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108">
+    <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" t="s">
-        <v>145</v>
-      </c>
-      <c r="D108" t="s">
-        <v>146</v>
-      </c>
-      <c r="E108" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" t="s">
-        <v>152</v>
-      </c>
-      <c r="G108" t="s">
-        <v>14</v>
-      </c>
-      <c r="H108" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -4192,16 +4291,16 @@
         <v>9</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>14</v>
@@ -4213,36 +4312,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110">
+    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" t="s">
-        <v>154</v>
-      </c>
-      <c r="D110" t="s">
-        <v>155</v>
-      </c>
-      <c r="E110" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="B110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D110" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -4250,57 +4349,57 @@
         <v>9</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" t="s">
-        <v>154</v>
-      </c>
-      <c r="D112" t="s">
-        <v>155</v>
-      </c>
-      <c r="E112" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" t="s">
-        <v>158</v>
-      </c>
-      <c r="G112" t="s">
-        <v>14</v>
-      </c>
-      <c r="H112" t="s">
-        <v>15</v>
-      </c>
-      <c r="I112" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -4308,16 +4407,16 @@
         <v>9</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>14</v>
@@ -4329,36 +4428,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114">
+    <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" t="s">
-        <v>154</v>
-      </c>
-      <c r="D114" t="s">
-        <v>155</v>
-      </c>
-      <c r="E114" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" t="s">
-        <v>160</v>
-      </c>
-      <c r="G114" t="s">
-        <v>14</v>
-      </c>
-      <c r="H114" t="s">
-        <v>15</v>
-      </c>
-      <c r="I114" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -4366,16 +4465,16 @@
         <v>9</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>14</v>
@@ -4387,36 +4486,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116">
+    <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" t="s">
-        <v>154</v>
-      </c>
-      <c r="D116" t="s">
-        <v>155</v>
-      </c>
-      <c r="E116" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" t="s">
-        <v>162</v>
-      </c>
-      <c r="G116" t="s">
-        <v>14</v>
-      </c>
-      <c r="H116" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -4424,16 +4523,16 @@
         <v>9</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>14</v>
@@ -4445,36 +4544,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118">
+    <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" t="s">
-        <v>154</v>
-      </c>
-      <c r="D118" t="s">
-        <v>155</v>
-      </c>
-      <c r="E118" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>14</v>
-      </c>
-      <c r="H118" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -4482,16 +4581,16 @@
         <v>9</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>14</v>
@@ -4503,36 +4602,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120">
+    <row r="120" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" t="s">
-        <v>154</v>
-      </c>
-      <c r="D120" t="s">
-        <v>155</v>
-      </c>
-      <c r="E120" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" t="s">
-        <v>166</v>
-      </c>
-      <c r="G120" t="s">
-        <v>14</v>
-      </c>
-      <c r="H120" t="s">
-        <v>15</v>
-      </c>
-      <c r="I120" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -4540,16 +4639,16 @@
         <v>9</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>14</v>
@@ -4561,36 +4660,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122">
+    <row r="122" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
-        <v>9</v>
-      </c>
-      <c r="C122" t="s">
-        <v>154</v>
-      </c>
-      <c r="D122" t="s">
-        <v>155</v>
-      </c>
-      <c r="E122" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" t="s">
-        <v>168</v>
-      </c>
-      <c r="G122" t="s">
-        <v>14</v>
-      </c>
-      <c r="H122" t="s">
-        <v>15</v>
-      </c>
-      <c r="I122" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -4598,16 +4697,16 @@
         <v>9</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>14</v>
@@ -4619,36 +4718,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124">
+    <row r="124" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" t="s">
-        <v>154</v>
-      </c>
-      <c r="D124" t="s">
-        <v>155</v>
-      </c>
-      <c r="E124" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" t="s">
-        <v>170</v>
-      </c>
-      <c r="G124" t="s">
-        <v>14</v>
-      </c>
-      <c r="H124" t="s">
-        <v>15</v>
-      </c>
-      <c r="I124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -4656,16 +4755,16 @@
         <v>9</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>14</v>
@@ -4677,36 +4776,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126">
+    <row r="126" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" t="s">
-        <v>154</v>
-      </c>
-      <c r="D126" t="s">
-        <v>155</v>
-      </c>
-      <c r="E126" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" t="s">
-        <v>172</v>
-      </c>
-      <c r="G126" t="s">
-        <v>14</v>
-      </c>
-      <c r="H126" t="s">
-        <v>15</v>
-      </c>
-      <c r="I126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -4714,16 +4813,16 @@
         <v>9</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>14</v>
@@ -4735,36 +4834,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128">
+    <row r="128" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
-        <v>9</v>
-      </c>
-      <c r="C128" t="s">
-        <v>154</v>
-      </c>
-      <c r="D128" t="s">
-        <v>155</v>
-      </c>
-      <c r="E128" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" t="s">
-        <v>174</v>
-      </c>
-      <c r="G128" t="s">
-        <v>14</v>
-      </c>
-      <c r="H128" t="s">
-        <v>15</v>
-      </c>
-      <c r="I128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -4772,16 +4871,16 @@
         <v>9</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>14</v>
@@ -4793,36 +4892,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130">
+    <row r="130" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130" t="s">
-        <v>154</v>
-      </c>
-      <c r="D130" t="s">
-        <v>155</v>
-      </c>
-      <c r="E130" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" t="s">
-        <v>176</v>
-      </c>
-      <c r="G130" t="s">
-        <v>14</v>
-      </c>
-      <c r="H130" t="s">
-        <v>15</v>
-      </c>
-      <c r="I130" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -4830,16 +4929,16 @@
         <v>9</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>14</v>
@@ -4851,36 +4950,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132">
+    <row r="132" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
-        <v>9</v>
-      </c>
-      <c r="C132" t="s">
-        <v>154</v>
-      </c>
-      <c r="D132" t="s">
-        <v>155</v>
-      </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" t="s">
-        <v>178</v>
-      </c>
-      <c r="G132" t="s">
-        <v>14</v>
-      </c>
-      <c r="H132" t="s">
-        <v>15</v>
-      </c>
-      <c r="I132" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -4888,16 +4987,16 @@
         <v>9</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>14</v>
@@ -4909,36 +5008,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134">
+    <row r="134" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
-        <v>9</v>
-      </c>
-      <c r="C134" t="s">
-        <v>154</v>
-      </c>
-      <c r="D134" t="s">
-        <v>155</v>
-      </c>
-      <c r="E134" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" t="s">
-        <v>180</v>
-      </c>
-      <c r="G134" t="s">
-        <v>14</v>
-      </c>
-      <c r="H134" t="s">
-        <v>15</v>
-      </c>
-      <c r="I134" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -4946,16 +5045,16 @@
         <v>9</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>14</v>
@@ -4967,36 +5066,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136">
+    <row r="136" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" t="s">
-        <v>154</v>
-      </c>
-      <c r="D136" t="s">
-        <v>155</v>
-      </c>
-      <c r="E136" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" t="s">
-        <v>182</v>
-      </c>
-      <c r="G136" t="s">
-        <v>14</v>
-      </c>
-      <c r="H136" t="s">
-        <v>15</v>
-      </c>
-      <c r="I136" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -5004,16 +5103,16 @@
         <v>9</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>14</v>
@@ -5025,36 +5124,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138">
+    <row r="138" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
-        <v>9</v>
-      </c>
-      <c r="C138" t="s">
-        <v>154</v>
-      </c>
-      <c r="D138" t="s">
-        <v>155</v>
-      </c>
-      <c r="E138" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="B138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G138" t="s">
-        <v>14</v>
-      </c>
-      <c r="H138" t="s">
-        <v>15</v>
-      </c>
-      <c r="I138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D138" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -5062,57 +5161,57 @@
         <v>9</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F139" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>139</v>
-      </c>
-      <c r="B140" t="s">
-        <v>9</v>
-      </c>
-      <c r="C140" t="s">
-        <v>154</v>
-      </c>
-      <c r="D140" t="s">
-        <v>155</v>
-      </c>
-      <c r="E140" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" t="s">
-        <v>186</v>
-      </c>
-      <c r="G140" t="s">
-        <v>14</v>
-      </c>
-      <c r="H140" t="s">
-        <v>15</v>
-      </c>
-      <c r="I140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -5120,16 +5219,16 @@
         <v>9</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>14</v>
@@ -5141,36 +5240,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142">
+    <row r="142" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
-        <v>9</v>
-      </c>
-      <c r="C142" t="s">
-        <v>188</v>
-      </c>
-      <c r="D142" t="s">
-        <v>189</v>
-      </c>
-      <c r="E142" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" t="s">
-        <v>190</v>
-      </c>
-      <c r="G142" t="s">
-        <v>14</v>
-      </c>
-      <c r="H142" t="s">
-        <v>15</v>
-      </c>
-      <c r="I142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -5178,16 +5277,16 @@
         <v>9</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>14</v>
@@ -5199,36 +5298,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144">
+    <row r="144" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144" t="s">
-        <v>188</v>
-      </c>
-      <c r="D144" t="s">
-        <v>189</v>
-      </c>
-      <c r="E144" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" t="s">
-        <v>192</v>
-      </c>
-      <c r="G144" t="s">
-        <v>14</v>
-      </c>
-      <c r="H144" t="s">
-        <v>15</v>
-      </c>
-      <c r="I144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B144" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -5236,16 +5335,16 @@
         <v>9</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>14</v>
@@ -5257,36 +5356,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146">
+    <row r="146" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" t="s">
-        <v>188</v>
-      </c>
-      <c r="D146" t="s">
-        <v>189</v>
-      </c>
-      <c r="E146" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" t="s">
-        <v>194</v>
-      </c>
-      <c r="G146" t="s">
-        <v>14</v>
-      </c>
-      <c r="H146" t="s">
-        <v>15</v>
-      </c>
-      <c r="I146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B146" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -5294,16 +5393,16 @@
         <v>9</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>14</v>
@@ -5315,37 +5414,617 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148">
+    <row r="148" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
-        <v>9</v>
-      </c>
-      <c r="C148" t="s">
-        <v>188</v>
-      </c>
-      <c r="D148" t="s">
-        <v>189</v>
-      </c>
-      <c r="E148" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" t="s">
-        <v>196</v>
-      </c>
-      <c r="G148" t="s">
-        <v>14</v>
-      </c>
-      <c r="H148" t="s">
-        <v>15</v>
-      </c>
-      <c r="I148" t="s">
-        <v>197</v>
+      <c r="B148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I168"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -5353,51 +6032,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>229</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="B4">
-        <v>147</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>233</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="B8">
         <v>78</v>
@@ -5405,48 +6105,74 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="B9">
         <v>39</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="4"/>
+        <v>237</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="4">
-        <v>9</v>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
